--- a/newui_Greyform/tmp/PBU_TERRAHL2_1.xlsx
+++ b/newui_Greyform/tmp/PBU_TERRAHL2_1.xlsx
@@ -4181,7 +4181,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-11-10 08:13:30</t>
+          <t>2025-11-11 02:07:39</t>
         </is>
       </c>
     </row>
